--- a/artfynd/A 2440-2023 artfynd.xlsx
+++ b/artfynd/A 2440-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139079</v>
+        <v>121139138</v>
       </c>
       <c r="B2" t="n">
-        <v>94844</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334475</v>
+        <v>334462</v>
       </c>
       <c r="R2" t="n">
-        <v>6403709</v>
+        <v>6403707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139138</v>
+        <v>121138794</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>58208</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,32 +807,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334462</v>
+        <v>334446</v>
       </c>
       <c r="R3" t="n">
-        <v>6403707</v>
+        <v>6403731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +876,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121138794</v>
+        <v>121139079</v>
       </c>
       <c r="B4" t="n">
-        <v>58205</v>
+        <v>94854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,32 +918,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334446</v>
+        <v>334475</v>
       </c>
       <c r="R4" t="n">
-        <v>6403731</v>
+        <v>6403709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 2440-2023 artfynd.xlsx
+++ b/artfynd/A 2440-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139138</v>
+        <v>121138794</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>58208</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334462</v>
+        <v>334446</v>
       </c>
       <c r="R2" t="n">
-        <v>6403707</v>
+        <v>6403731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121138794</v>
+        <v>121139138</v>
       </c>
       <c r="B3" t="n">
-        <v>58208</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,32 +802,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334446</v>
+        <v>334462</v>
       </c>
       <c r="R3" t="n">
-        <v>6403731</v>
+        <v>6403707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2440-2023 artfynd.xlsx
+++ b/artfynd/A 2440-2023 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>121139079</v>
       </c>
       <c r="B4" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2440-2023 artfynd.xlsx
+++ b/artfynd/A 2440-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121138794</v>
+        <v>121139138</v>
       </c>
       <c r="B2" t="n">
-        <v>58208</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334446</v>
+        <v>334462</v>
       </c>
       <c r="R2" t="n">
-        <v>6403731</v>
+        <v>6403707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139138</v>
+        <v>121139079</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>94867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,32 +807,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334462</v>
+        <v>334475</v>
       </c>
       <c r="R3" t="n">
-        <v>6403707</v>
+        <v>6403709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,11 +875,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121139079</v>
+        <v>121138794</v>
       </c>
       <c r="B4" t="n">
-        <v>94866</v>
+        <v>58208</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,31 +917,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334475</v>
+        <v>334446</v>
       </c>
       <c r="R4" t="n">
-        <v>6403709</v>
+        <v>6403731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 2440-2023 artfynd.xlsx
+++ b/artfynd/A 2440-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139138</v>
+        <v>121139079</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>94870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334462</v>
+        <v>334475</v>
       </c>
       <c r="R2" t="n">
-        <v>6403707</v>
+        <v>6403709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139079</v>
+        <v>121138794</v>
       </c>
       <c r="B3" t="n">
-        <v>94867</v>
+        <v>58211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,31 +801,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334475</v>
+        <v>334446</v>
       </c>
       <c r="R3" t="n">
-        <v>6403709</v>
+        <v>6403731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121138794</v>
+        <v>121139138</v>
       </c>
       <c r="B4" t="n">
-        <v>58208</v>
+        <v>8424</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,32 +912,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334446</v>
+        <v>334462</v>
       </c>
       <c r="R4" t="n">
-        <v>6403731</v>
+        <v>6403707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,6 +981,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2440-2023 artfynd.xlsx
+++ b/artfynd/A 2440-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121139079</v>
       </c>
       <c r="B2" t="n">
-        <v>94870</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121138794</v>
+        <v>130624929</v>
       </c>
       <c r="B3" t="n">
-        <v>58211</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>101002</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ädelguldbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gnorimus nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,23 +814,31 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>pheromone</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lerum, Vg</t>
+          <t>Gullringsbo, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334446</v>
+        <v>334430</v>
       </c>
       <c r="R3" t="n">
-        <v>6403731</v>
+        <v>6403853</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +862,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bifångst i feromonfälla.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,18 +881,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Rostedt</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -899,12 +903,7 @@
         <v>121139138</v>
       </c>
       <c r="B4" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,6 +1009,449 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121139139</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lerum, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334297</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6403810</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Rostedt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126439365</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hagaberget, Hagaberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334467</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6403773</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Tjärnberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Tjärnberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121138794</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lerum, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334446</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6403731</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Rostedt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121138862</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lerum, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>334472</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6403675</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Rostedt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2440-2023 artfynd.xlsx
+++ b/artfynd/A 2440-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139079</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130624929</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139138</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139139</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126439365</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121138794</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,8 +1486,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121138862</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>